--- a/ReportingFrameworks.xlsx
+++ b/ReportingFrameworks.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CRISTIANANTON.CALIN\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8e8881838485c825/Documents/Sustainability And Reporting IFoA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B52AE6F2-4AAD-4B6E-B8BC-3465C5A91BBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{B52AE6F2-4AAD-4B6E-B8BC-3465C5A91BBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F4F00DB-AEE1-433D-9BEB-8B79F22753E9}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C0644C4C-7BC9-4CA8-A6AC-F86593A58991}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{C0644C4C-7BC9-4CA8-A6AC-F86593A58991}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$569</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$701</definedName>
   </definedNames>
   <calcPr calcId="191029" calcOnSave="0"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3931" uniqueCount="1432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3931" uniqueCount="1431">
   <si>
     <t>Framework</t>
   </si>
@@ -4968,9 +4968,6 @@
   </si>
   <si>
     <t>SBTi</t>
-  </si>
-  <si>
-    <t>Metrics and Targets</t>
   </si>
   <si>
     <t>FINZ-C1</t>
@@ -5809,6 +5806,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6128,16 +6129,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F4B9D16-0649-4346-A6A6-AF198B8A35D8}">
-  <dimension ref="A1:G701"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:H701"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="11.75" customWidth="1"/>
-    <col min="4" max="4" width="81.33203125" customWidth="1"/>
+    <col min="4" max="4" width="81.375" customWidth="1"/>
     <col min="5" max="6" width="11.75" customWidth="1"/>
-    <col min="7" max="7" width="65.33203125" customWidth="1"/>
+    <col min="7" max="7" width="65.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6160,7 +6162,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -6183,7 +6185,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -6206,7 +6208,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -6229,7 +6231,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -6252,7 +6254,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -6275,7 +6277,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -6298,7 +6300,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -6321,7 +6323,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -6344,7 +6346,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -6367,7 +6369,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -6390,7 +6392,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>6</v>
       </c>
@@ -6413,7 +6415,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>6</v>
       </c>
@@ -6436,7 +6438,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>6</v>
       </c>
@@ -6459,7 +6461,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -6482,7 +6484,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>6</v>
       </c>
@@ -6505,7 +6507,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -6528,7 +6530,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>6</v>
       </c>
@@ -6551,7 +6553,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>6</v>
       </c>
@@ -6574,7 +6576,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>6</v>
       </c>
@@ -6597,7 +6599,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -6620,7 +6622,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>6</v>
       </c>
@@ -6643,7 +6645,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>6</v>
       </c>
@@ -6666,7 +6668,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>6</v>
       </c>
@@ -6689,7 +6691,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>6</v>
       </c>
@@ -6712,7 +6714,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>6</v>
       </c>
@@ -6735,7 +6737,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>6</v>
       </c>
@@ -6758,7 +6760,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>6</v>
       </c>
@@ -6781,7 +6783,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>6</v>
       </c>
@@ -6804,7 +6806,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>6</v>
       </c>
@@ -6827,7 +6829,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>6</v>
       </c>
@@ -6850,7 +6852,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>6</v>
       </c>
@@ -6873,7 +6875,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>6</v>
       </c>
@@ -6896,7 +6898,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>6</v>
       </c>
@@ -6919,7 +6921,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>6</v>
       </c>
@@ -6942,7 +6944,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>6</v>
       </c>
@@ -6965,7 +6967,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>6</v>
       </c>
@@ -6988,7 +6990,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>6</v>
       </c>
@@ -7011,7 +7013,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>6</v>
       </c>
@@ -7034,7 +7036,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>6</v>
       </c>
@@ -7057,7 +7059,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>6</v>
       </c>
@@ -7080,7 +7082,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>6</v>
       </c>
@@ -7103,7 +7105,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>6</v>
       </c>
@@ -7126,7 +7128,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>6</v>
       </c>
@@ -7149,7 +7151,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>6</v>
       </c>
@@ -7172,7 +7174,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>6</v>
       </c>
@@ -7195,7 +7197,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>6</v>
       </c>
@@ -7218,7 +7220,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>6</v>
       </c>
@@ -7241,7 +7243,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>6</v>
       </c>
@@ -7264,7 +7266,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>6</v>
       </c>
@@ -7287,7 +7289,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>6</v>
       </c>
@@ -7310,7 +7312,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>6</v>
       </c>
@@ -7333,7 +7335,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>6</v>
       </c>
@@ -7356,7 +7358,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>6</v>
       </c>
@@ -7379,7 +7381,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>6</v>
       </c>
@@ -7402,7 +7404,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>6</v>
       </c>
@@ -7425,7 +7427,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>6</v>
       </c>
@@ -7448,7 +7450,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>6</v>
       </c>
@@ -7471,7 +7473,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>6</v>
       </c>
@@ -7494,7 +7496,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>76</v>
       </c>
@@ -7517,7 +7519,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>76</v>
       </c>
@@ -7540,7 +7542,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>76</v>
       </c>
@@ -7563,7 +7565,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>76</v>
       </c>
@@ -7586,7 +7588,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>76</v>
       </c>
@@ -7609,7 +7611,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>76</v>
       </c>
@@ -7632,7 +7634,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>76</v>
       </c>
@@ -7655,7 +7657,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>76</v>
       </c>
@@ -7678,7 +7680,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>76</v>
       </c>
@@ -7701,7 +7703,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>76</v>
       </c>
@@ -7724,7 +7726,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>76</v>
       </c>
@@ -7747,7 +7749,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>76</v>
       </c>
@@ -7770,7 +7772,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>76</v>
       </c>
@@ -7793,7 +7795,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>76</v>
       </c>
@@ -7816,7 +7818,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>76</v>
       </c>
@@ -7839,7 +7841,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>76</v>
       </c>
@@ -7862,7 +7864,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>76</v>
       </c>
@@ -7885,7 +7887,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>76</v>
       </c>
@@ -7908,7 +7910,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>76</v>
       </c>
@@ -7931,7 +7933,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>76</v>
       </c>
@@ -7954,7 +7956,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>76</v>
       </c>
@@ -7977,7 +7979,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>76</v>
       </c>
@@ -8000,7 +8002,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>76</v>
       </c>
@@ -8023,7 +8025,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>76</v>
       </c>
@@ -8046,7 +8048,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7" ht="15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>76</v>
       </c>
@@ -8069,7 +8071,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>76</v>
       </c>
@@ -8092,7 +8094,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>76</v>
       </c>
@@ -8115,7 +8117,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>76</v>
       </c>
@@ -8138,7 +8140,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>76</v>
       </c>
@@ -8161,7 +8163,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>76</v>
       </c>
@@ -8184,7 +8186,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>76</v>
       </c>
@@ -8207,7 +8209,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
         <v>76</v>
       </c>
@@ -8230,7 +8232,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>76</v>
       </c>
@@ -8253,7 +8255,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>76</v>
       </c>
@@ -8276,7 +8278,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>76</v>
       </c>
@@ -8299,7 +8301,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>76</v>
       </c>
@@ -8322,7 +8324,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>76</v>
       </c>
@@ -8345,7 +8347,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>76</v>
       </c>
@@ -8368,7 +8370,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>76</v>
       </c>
@@ -8391,7 +8393,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>76</v>
       </c>
@@ -8414,7 +8416,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>76</v>
       </c>
@@ -8437,7 +8439,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>76</v>
       </c>
@@ -8460,7 +8462,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>76</v>
       </c>
@@ -8483,7 +8485,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>76</v>
       </c>
@@ -8506,7 +8508,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>76</v>
       </c>
@@ -8529,7 +8531,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>76</v>
       </c>
@@ -8552,7 +8554,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>76</v>
       </c>
@@ -8575,7 +8577,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>76</v>
       </c>
@@ -8598,7 +8600,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>76</v>
       </c>
@@ -8621,7 +8623,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>76</v>
       </c>
@@ -8644,7 +8646,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>76</v>
       </c>
@@ -8667,7 +8669,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>76</v>
       </c>
@@ -8690,7 +8692,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>76</v>
       </c>
@@ -8713,7 +8715,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>76</v>
       </c>
@@ -8736,7 +8738,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>76</v>
       </c>
@@ -8759,7 +8761,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>76</v>
       </c>
@@ -8782,7 +8784,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>264</v>
       </c>
@@ -8800,7 +8802,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>264</v>
       </c>
@@ -8818,7 +8820,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>264</v>
       </c>
@@ -8836,7 +8838,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>264</v>
       </c>
@@ -8854,7 +8856,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>264</v>
       </c>
@@ -8872,7 +8874,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>264</v>
       </c>
@@ -8890,7 +8892,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>264</v>
       </c>
@@ -8908,7 +8910,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>264</v>
       </c>
@@ -8926,7 +8928,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>264</v>
       </c>
@@ -8944,7 +8946,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>264</v>
       </c>
@@ -8962,7 +8964,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>264</v>
       </c>
@@ -8980,7 +8982,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>264</v>
       </c>
@@ -8998,7 +9000,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>264</v>
       </c>
@@ -9016,7 +9018,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
         <v>264</v>
       </c>
@@ -9034,7 +9036,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
         <v>264</v>
       </c>
@@ -9052,7 +9054,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
         <v>264</v>
       </c>
@@ -9070,7 +9072,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>264</v>
       </c>
@@ -9088,7 +9090,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
         <v>264</v>
       </c>
@@ -9106,7 +9108,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
         <v>264</v>
       </c>
@@ -9124,7 +9126,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
         <v>264</v>
       </c>
@@ -9142,7 +9144,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
         <v>264</v>
       </c>
@@ -9160,7 +9162,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
         <v>264</v>
       </c>
@@ -9178,7 +9180,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
         <v>264</v>
       </c>
@@ -9196,7 +9198,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
         <v>264</v>
       </c>
@@ -9214,7 +9216,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
         <v>264</v>
       </c>
@@ -9232,7 +9234,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>264</v>
       </c>
@@ -9250,7 +9252,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
         <v>264</v>
       </c>
@@ -9268,7 +9270,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
         <v>264</v>
       </c>
@@ -9286,7 +9288,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
         <v>264</v>
       </c>
@@ -9304,7 +9306,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
         <v>264</v>
       </c>
@@ -9322,7 +9324,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
         <v>264</v>
       </c>
@@ -9340,7 +9342,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
         <v>264</v>
       </c>
@@ -9358,7 +9360,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
         <v>264</v>
       </c>
@@ -9376,7 +9378,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
         <v>264</v>
       </c>
@@ -9394,7 +9396,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
         <v>264</v>
       </c>
@@ -9412,7 +9414,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
         <v>264</v>
       </c>
@@ -9430,7 +9432,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
         <v>264</v>
       </c>
@@ -9448,7 +9450,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
         <v>264</v>
       </c>
@@ -9466,7 +9468,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
         <v>264</v>
       </c>
@@ -9484,7 +9486,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>264</v>
       </c>
@@ -9502,7 +9504,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>264</v>
       </c>
@@ -9520,7 +9522,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>264</v>
       </c>
@@ -9538,7 +9540,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>264</v>
       </c>
@@ -9556,7 +9558,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>264</v>
       </c>
@@ -9574,7 +9576,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
         <v>264</v>
       </c>
@@ -9592,7 +9594,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
         <v>264</v>
       </c>
@@ -9610,7 +9612,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
         <v>264</v>
       </c>
@@ -9628,7 +9630,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>264</v>
       </c>
@@ -9646,7 +9648,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>264</v>
       </c>
@@ -9664,7 +9666,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
         <v>264</v>
       </c>
@@ -9682,7 +9684,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
         <v>264</v>
       </c>
@@ -9700,7 +9702,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
         <v>264</v>
       </c>
@@ -9718,7 +9720,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
         <v>264</v>
       </c>
@@ -9736,7 +9738,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
         <v>264</v>
       </c>
@@ -9754,7 +9756,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>264</v>
       </c>
@@ -9772,7 +9774,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
         <v>264</v>
       </c>
@@ -9790,7 +9792,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
         <v>264</v>
       </c>
@@ -9808,7 +9810,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
         <v>264</v>
       </c>
@@ -9826,7 +9828,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>264</v>
       </c>
@@ -9844,7 +9846,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
         <v>264</v>
       </c>
@@ -9862,7 +9864,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>264</v>
       </c>
@@ -9880,7 +9882,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>264</v>
       </c>
@@ -9898,7 +9900,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>264</v>
       </c>
@@ -9916,7 +9918,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>264</v>
       </c>
@@ -9934,7 +9936,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
         <v>264</v>
       </c>
@@ -9952,7 +9954,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>264</v>
       </c>
@@ -9970,7 +9972,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>264</v>
       </c>
@@ -9988,7 +9990,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>264</v>
       </c>
@@ -10006,7 +10008,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
         <v>264</v>
       </c>
@@ -10024,7 +10026,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
         <v>264</v>
       </c>
@@ -10042,7 +10044,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
         <v>264</v>
       </c>
@@ -10060,7 +10062,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
         <v>264</v>
       </c>
@@ -10078,7 +10080,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
         <v>264</v>
       </c>
@@ -10096,7 +10098,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
         <v>264</v>
       </c>
@@ -10114,7 +10116,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>264</v>
       </c>
@@ -10132,7 +10134,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
         <v>264</v>
       </c>
@@ -10150,7 +10152,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
         <v>264</v>
       </c>
@@ -10168,7 +10170,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>264</v>
       </c>
@@ -10186,7 +10188,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>264</v>
       </c>
@@ -10204,7 +10206,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>264</v>
       </c>
@@ -10222,7 +10224,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>264</v>
       </c>
@@ -10240,7 +10242,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>264</v>
       </c>
@@ -10258,7 +10260,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>264</v>
       </c>
@@ -10276,7 +10278,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>264</v>
       </c>
@@ -10294,7 +10296,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>308</v>
       </c>
@@ -10312,7 +10314,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>308</v>
       </c>
@@ -10330,7 +10332,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>308</v>
       </c>
@@ -10348,7 +10350,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>308</v>
       </c>
@@ -10366,7 +10368,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>308</v>
       </c>
@@ -10384,7 +10386,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>308</v>
       </c>
@@ -10402,7 +10404,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>308</v>
       </c>
@@ -10420,7 +10422,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>308</v>
       </c>
@@ -10438,7 +10440,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>308</v>
       </c>
@@ -10456,7 +10458,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>308</v>
       </c>
@@ -10474,7 +10476,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>308</v>
       </c>
@@ -10492,7 +10494,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>308</v>
       </c>
@@ -10510,7 +10512,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>308</v>
       </c>
@@ -10528,7 +10530,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>308</v>
       </c>
@@ -10546,7 +10548,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>308</v>
       </c>
@@ -10564,7 +10566,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>308</v>
       </c>
@@ -10582,7 +10584,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>308</v>
       </c>
@@ -10600,7 +10602,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>308</v>
       </c>
@@ -10618,7 +10620,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>308</v>
       </c>
@@ -10636,7 +10638,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>308</v>
       </c>
@@ -10654,7 +10656,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>308</v>
       </c>
@@ -10672,7 +10674,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>308</v>
       </c>
@@ -10690,7 +10692,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>308</v>
       </c>
@@ -10708,7 +10710,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>308</v>
       </c>
@@ -10726,7 +10728,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>308</v>
       </c>
@@ -10744,7 +10746,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>308</v>
       </c>
@@ -10762,7 +10764,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>308</v>
       </c>
@@ -10780,7 +10782,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>308</v>
       </c>
@@ -10798,7 +10800,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>308</v>
       </c>
@@ -10816,7 +10818,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>308</v>
       </c>
@@ -10834,7 +10836,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>308</v>
       </c>
@@ -10852,7 +10854,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>308</v>
       </c>
@@ -10870,7 +10872,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>308</v>
       </c>
@@ -10888,7 +10890,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>308</v>
       </c>
@@ -10906,7 +10908,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>308</v>
       </c>
@@ -10924,7 +10926,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>308</v>
       </c>
@@ -10942,7 +10944,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
         <v>308</v>
       </c>
@@ -10960,7 +10962,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
         <v>308</v>
       </c>
@@ -10978,7 +10980,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>308</v>
       </c>
@@ -10996,7 +10998,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>308</v>
       </c>
@@ -11014,7 +11016,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>308</v>
       </c>
@@ -11032,7 +11034,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>308</v>
       </c>
@@ -11050,7 +11052,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>308</v>
       </c>
@@ -11068,7 +11070,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
         <v>308</v>
       </c>
@@ -11086,7 +11088,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>308</v>
       </c>
@@ -11104,7 +11106,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>308</v>
       </c>
@@ -11122,7 +11124,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>308</v>
       </c>
@@ -11140,7 +11142,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>308</v>
       </c>
@@ -11158,7 +11160,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
         <v>308</v>
       </c>
@@ -11176,7 +11178,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
         <v>308</v>
       </c>
@@ -11194,7 +11196,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
         <v>308</v>
       </c>
@@ -11212,7 +11214,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
         <v>308</v>
       </c>
@@ -11230,7 +11232,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
         <v>308</v>
       </c>
@@ -11248,7 +11250,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
         <v>308</v>
       </c>
@@ -11266,7 +11268,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
         <v>308</v>
       </c>
@@ -11284,7 +11286,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
         <v>308</v>
       </c>
@@ -11302,7 +11304,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
         <v>308</v>
       </c>
@@ -11320,7 +11322,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
         <v>308</v>
       </c>
@@ -11338,7 +11340,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
         <v>308</v>
       </c>
@@ -11356,7 +11358,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
         <v>308</v>
       </c>
@@ -11374,7 +11376,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
         <v>308</v>
       </c>
@@ -11392,7 +11394,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
         <v>431</v>
       </c>
@@ -11410,7 +11412,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
         <v>431</v>
       </c>
@@ -11428,7 +11430,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
         <v>431</v>
       </c>
@@ -11446,7 +11448,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
         <v>431</v>
       </c>
@@ -11464,7 +11466,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
         <v>431</v>
       </c>
@@ -11482,7 +11484,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
         <v>431</v>
       </c>
@@ -11500,7 +11502,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
         <v>431</v>
       </c>
@@ -11518,7 +11520,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
         <v>431</v>
       </c>
@@ -11536,7 +11538,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
         <v>431</v>
       </c>
@@ -11554,7 +11556,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
         <v>431</v>
       </c>
@@ -11572,7 +11574,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
         <v>431</v>
       </c>
@@ -11590,7 +11592,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
         <v>431</v>
       </c>
@@ -11608,7 +11610,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
         <v>431</v>
       </c>
@@ -11626,7 +11628,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
         <v>431</v>
       </c>
@@ -11644,7 +11646,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
         <v>431</v>
       </c>
@@ -11662,7 +11664,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
         <v>431</v>
       </c>
@@ -11680,7 +11682,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
         <v>431</v>
       </c>
@@ -11698,7 +11700,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
         <v>431</v>
       </c>
@@ -11716,7 +11718,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
         <v>431</v>
       </c>
@@ -11734,7 +11736,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
         <v>431</v>
       </c>
@@ -11752,7 +11754,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
         <v>431</v>
       </c>
@@ -11770,7 +11772,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
         <v>431</v>
       </c>
@@ -11788,7 +11790,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
         <v>431</v>
       </c>
@@ -11806,7 +11808,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
         <v>431</v>
       </c>
@@ -11824,7 +11826,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
         <v>431</v>
       </c>
@@ -11842,7 +11844,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
         <v>431</v>
       </c>
@@ -11860,7 +11862,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
         <v>431</v>
       </c>
@@ -11878,7 +11880,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
         <v>431</v>
       </c>
@@ -11896,7 +11898,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
         <v>431</v>
       </c>
@@ -11914,7 +11916,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
         <v>431</v>
       </c>
@@ -11932,7 +11934,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
         <v>431</v>
       </c>
@@ -11950,7 +11952,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
         <v>431</v>
       </c>
@@ -11968,7 +11970,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
         <v>431</v>
       </c>
@@ -11986,7 +11988,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
         <v>431</v>
       </c>
@@ -12004,7 +12006,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
         <v>431</v>
       </c>
@@ -12022,7 +12024,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
         <v>431</v>
       </c>
@@ -12040,7 +12042,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
         <v>431</v>
       </c>
@@ -12058,7 +12060,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
         <v>431</v>
       </c>
@@ -12076,7 +12078,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
         <v>431</v>
       </c>
@@ -12094,7 +12096,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
         <v>431</v>
       </c>
@@ -12112,7 +12114,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
         <v>431</v>
       </c>
@@ -12130,7 +12132,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
         <v>431</v>
       </c>
@@ -12148,7 +12150,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
         <v>431</v>
       </c>
@@ -12166,7 +12168,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
         <v>431</v>
       </c>
@@ -12184,7 +12186,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
         <v>431</v>
       </c>
@@ -12202,7 +12204,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
         <v>431</v>
       </c>
@@ -12220,7 +12222,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
         <v>431</v>
       </c>
@@ -12238,7 +12240,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
         <v>431</v>
       </c>
@@ -12256,7 +12258,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
         <v>431</v>
       </c>
@@ -12274,7 +12276,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
         <v>431</v>
       </c>
@@ -12292,7 +12294,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
         <v>431</v>
       </c>
@@ -12310,7 +12312,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
         <v>431</v>
       </c>
@@ -12328,7 +12330,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
         <v>431</v>
       </c>
@@ -12346,7 +12348,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
         <v>431</v>
       </c>
@@ -12364,7 +12366,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
         <v>431</v>
       </c>
@@ -12382,7 +12384,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
         <v>431</v>
       </c>
@@ -12400,7 +12402,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
         <v>431</v>
       </c>
@@ -12418,7 +12420,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
         <v>431</v>
       </c>
@@ -12436,7 +12438,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
         <v>431</v>
       </c>
@@ -12454,7 +12456,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
         <v>431</v>
       </c>
@@ -12472,7 +12474,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
         <v>431</v>
       </c>
@@ -12490,7 +12492,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
         <v>431</v>
       </c>
@@ -12508,7 +12510,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
         <v>431</v>
       </c>
@@ -12526,7 +12528,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
         <v>431</v>
       </c>
@@ -12544,7 +12546,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="325" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
         <v>431</v>
       </c>
@@ -12562,7 +12564,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
         <v>431</v>
       </c>
@@ -12580,7 +12582,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
         <v>431</v>
       </c>
@@ -12598,7 +12600,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="328" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
         <v>431</v>
       </c>
@@ -12616,7 +12618,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="329" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
         <v>431</v>
       </c>
@@ -12634,7 +12636,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
         <v>431</v>
       </c>
@@ -12652,7 +12654,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
         <v>570</v>
       </c>
@@ -12675,7 +12677,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="332" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
         <v>570</v>
       </c>
@@ -12698,7 +12700,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="333" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
         <v>570</v>
       </c>
@@ -12721,7 +12723,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
         <v>570</v>
       </c>
@@ -12744,7 +12746,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="335" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
         <v>570</v>
       </c>
@@ -12767,7 +12769,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
         <v>570</v>
       </c>
@@ -12790,7 +12792,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
         <v>570</v>
       </c>
@@ -12813,7 +12815,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
         <v>570</v>
       </c>
@@ -12836,7 +12838,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
         <v>570</v>
       </c>
@@ -12859,7 +12861,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
         <v>570</v>
       </c>
@@ -12882,7 +12884,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
         <v>570</v>
       </c>
@@ -12905,7 +12907,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="342" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
         <v>570</v>
       </c>
@@ -12928,7 +12930,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="343" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
         <v>570</v>
       </c>
@@ -12951,7 +12953,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="344" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
         <v>570</v>
       </c>
@@ -12974,7 +12976,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
         <v>570</v>
       </c>
@@ -12997,7 +12999,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="346" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
         <v>570</v>
       </c>
@@ -13020,7 +13022,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="347" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
         <v>570</v>
       </c>
@@ -13043,7 +13045,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="348" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
         <v>570</v>
       </c>
@@ -13066,7 +13068,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="349" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
         <v>570</v>
       </c>
@@ -13089,7 +13091,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="350" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
         <v>737</v>
       </c>
@@ -13106,7 +13108,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="351" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
         <v>737</v>
       </c>
@@ -13123,7 +13125,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="352" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
         <v>737</v>
       </c>
@@ -13140,7 +13142,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
         <v>737</v>
       </c>
@@ -13157,7 +13159,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
         <v>737</v>
       </c>
@@ -13174,7 +13176,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
         <v>737</v>
       </c>
@@ -13191,7 +13193,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
         <v>737</v>
       </c>
@@ -13208,7 +13210,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
         <v>737</v>
       </c>
@@ -13225,7 +13227,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="358" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
         <v>737</v>
       </c>
@@ -13242,7 +13244,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="359" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
         <v>737</v>
       </c>
@@ -13259,7 +13261,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="360" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
         <v>737</v>
       </c>
@@ -13276,7 +13278,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="361" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
         <v>737</v>
       </c>
@@ -13293,7 +13295,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="362" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
         <v>737</v>
       </c>
@@ -13310,7 +13312,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="363" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
         <v>737</v>
       </c>
@@ -13327,7 +13329,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="364" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
         <v>737</v>
       </c>
@@ -13344,7 +13346,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="365" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
         <v>737</v>
       </c>
@@ -13361,7 +13363,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="366" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
         <v>737</v>
       </c>
@@ -13378,7 +13380,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="367" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
         <v>737</v>
       </c>
@@ -13395,7 +13397,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
         <v>737</v>
       </c>
@@ -13412,7 +13414,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
         <v>737</v>
       </c>
@@ -13429,7 +13431,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
         <v>737</v>
       </c>
@@ -13446,7 +13448,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
         <v>737</v>
       </c>
@@ -13463,7 +13465,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
         <v>737</v>
       </c>
@@ -13480,7 +13482,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
         <v>737</v>
       </c>
@@ -13497,7 +13499,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
         <v>737</v>
       </c>
@@ -13514,7 +13516,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
         <v>737</v>
       </c>
@@ -13531,7 +13533,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
         <v>737</v>
       </c>
@@ -13548,7 +13550,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
         <v>737</v>
       </c>
@@ -13565,7 +13567,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
         <v>737</v>
       </c>
@@ -13582,7 +13584,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
         <v>737</v>
       </c>
@@ -13599,7 +13601,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
         <v>737</v>
       </c>
@@ -13616,7 +13618,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="381" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
         <v>737</v>
       </c>
@@ -13633,7 +13635,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="382" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
         <v>737</v>
       </c>
@@ -13650,7 +13652,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="383" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
         <v>737</v>
       </c>
@@ -13667,7 +13669,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="384" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
         <v>737</v>
       </c>
@@ -13684,7 +13686,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="385" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
         <v>737</v>
       </c>
@@ -13701,7 +13703,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="386" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A386" t="s">
         <v>737</v>
       </c>
@@ -13718,7 +13720,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="387" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
         <v>737</v>
       </c>
@@ -13735,7 +13737,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="388" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
         <v>737</v>
       </c>
@@ -13752,7 +13754,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="389" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
         <v>737</v>
       </c>
@@ -13769,7 +13771,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="390" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
         <v>737</v>
       </c>
@@ -13786,7 +13788,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="391" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A391" t="s">
         <v>737</v>
       </c>
@@ -13803,7 +13805,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="392" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
         <v>737</v>
       </c>
@@ -13820,7 +13822,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="393" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
         <v>737</v>
       </c>
@@ -13837,7 +13839,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="394" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
         <v>737</v>
       </c>
@@ -13854,7 +13856,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="395" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
         <v>737</v>
       </c>
@@ -13871,7 +13873,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="396" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
         <v>737</v>
       </c>
@@ -13888,7 +13890,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="397" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
         <v>737</v>
       </c>
@@ -13905,7 +13907,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="398" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
         <v>737</v>
       </c>
@@ -13922,7 +13924,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="399" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
         <v>737</v>
       </c>
@@ -13939,7 +13941,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="400" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
         <v>737</v>
       </c>
@@ -13956,7 +13958,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="401" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
         <v>737</v>
       </c>
@@ -13973,7 +13975,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
         <v>737</v>
       </c>
@@ -13990,7 +13992,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
         <v>737</v>
       </c>
@@ -14007,7 +14009,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
         <v>737</v>
       </c>
@@ -14024,7 +14026,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
         <v>737</v>
       </c>
@@ -14041,7 +14043,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
         <v>737</v>
       </c>
@@ -14058,7 +14060,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="407" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
         <v>737</v>
       </c>
@@ -14075,7 +14077,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="408" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
         <v>737</v>
       </c>
@@ -14092,7 +14094,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="409" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
         <v>773</v>
       </c>
@@ -14109,7 +14111,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
         <v>773</v>
       </c>
@@ -14126,7 +14128,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="411" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
         <v>773</v>
       </c>
@@ -14143,7 +14145,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="412" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
         <v>773</v>
       </c>
@@ -14160,7 +14162,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="413" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
         <v>773</v>
       </c>
@@ -14177,7 +14179,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="414" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
         <v>773</v>
       </c>
@@ -14194,7 +14196,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="415" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
         <v>773</v>
       </c>
@@ -14211,7 +14213,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="416" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
         <v>773</v>
       </c>
@@ -14228,7 +14230,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="417" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
         <v>773</v>
       </c>
@@ -14245,7 +14247,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="418" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
         <v>773</v>
       </c>
@@ -14262,7 +14264,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="419" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
         <v>773</v>
       </c>
@@ -14279,7 +14281,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="420" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
         <v>773</v>
       </c>
@@ -14296,7 +14298,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="421" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
         <v>773</v>
       </c>
@@ -14313,7 +14315,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="422" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
         <v>773</v>
       </c>
@@ -14330,7 +14332,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="423" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A423" t="s">
         <v>773</v>
       </c>
@@ -14347,7 +14349,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="424" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A424" t="s">
         <v>773</v>
       </c>
@@ -14364,7 +14366,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="425" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
         <v>773</v>
       </c>
@@ -14381,7 +14383,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="426" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
         <v>773</v>
       </c>
@@ -14398,7 +14400,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="427" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
         <v>773</v>
       </c>
@@ -14415,7 +14417,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="428" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
         <v>773</v>
       </c>
@@ -14432,7 +14434,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="429" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
         <v>773</v>
       </c>
@@ -14449,7 +14451,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="430" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
         <v>773</v>
       </c>
@@ -14466,7 +14468,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="431" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A431" t="s">
         <v>773</v>
       </c>
@@ -14483,7 +14485,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="432" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A432" t="s">
         <v>773</v>
       </c>
@@ -14500,7 +14502,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="433" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
         <v>773</v>
       </c>
@@ -14517,7 +14519,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="434" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A434" t="s">
         <v>773</v>
       </c>
@@ -14534,7 +14536,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="435" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A435" t="s">
         <v>773</v>
       </c>
@@ -14551,7 +14553,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="436" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A436" t="s">
         <v>773</v>
       </c>
@@ -14568,7 +14570,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="437" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A437" t="s">
         <v>773</v>
       </c>
@@ -14585,7 +14587,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="438" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A438" t="s">
         <v>773</v>
       </c>
@@ -14602,7 +14604,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="439" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A439" t="s">
         <v>773</v>
       </c>
@@ -14619,7 +14621,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="440" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A440" t="s">
         <v>773</v>
       </c>
@@ -14636,7 +14638,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="441" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
         <v>773</v>
       </c>
@@ -14653,7 +14655,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="442" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
         <v>774</v>
       </c>
@@ -14670,7 +14672,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="443" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
         <v>774</v>
       </c>
@@ -14690,7 +14692,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="444" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A444" t="s">
         <v>774</v>
       </c>
@@ -14707,7 +14709,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="445" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
         <v>774</v>
       </c>
@@ -14727,7 +14729,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="446" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
         <v>774</v>
       </c>
@@ -14747,7 +14749,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="447" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A447" t="s">
         <v>774</v>
       </c>
@@ -14767,7 +14769,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="448" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
         <v>774</v>
       </c>
@@ -14787,7 +14789,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="449" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
         <v>774</v>
       </c>
@@ -14807,7 +14809,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="450" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
         <v>774</v>
       </c>
@@ -14827,7 +14829,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="451" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A451" t="s">
         <v>774</v>
       </c>
@@ -14847,7 +14849,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="452" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A452" t="s">
         <v>774</v>
       </c>
@@ -14864,7 +14866,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="453" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A453" t="s">
         <v>774</v>
       </c>
@@ -14881,7 +14883,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="454" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
         <v>774</v>
       </c>
@@ -14898,7 +14900,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="455" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A455" t="s">
         <v>774</v>
       </c>
@@ -14918,7 +14920,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="456" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A456" t="s">
         <v>774</v>
       </c>
@@ -14935,7 +14937,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="457" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A457" t="s">
         <v>774</v>
       </c>
@@ -14955,7 +14957,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="458" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A458" t="s">
         <v>774</v>
       </c>
@@ -14975,7 +14977,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="459" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A459" t="s">
         <v>774</v>
       </c>
@@ -14995,7 +14997,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="460" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A460" t="s">
         <v>774</v>
       </c>
@@ -15012,7 +15014,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="461" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A461" t="s">
         <v>774</v>
       </c>
@@ -15029,7 +15031,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="462" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A462" t="s">
         <v>774</v>
       </c>
@@ -15049,7 +15051,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="463" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A463" t="s">
         <v>774</v>
       </c>
@@ -15066,7 +15068,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="464" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A464" t="s">
         <v>774</v>
       </c>
@@ -15083,7 +15085,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="465" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A465" t="s">
         <v>774</v>
       </c>
@@ -15103,7 +15105,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="466" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A466" t="s">
         <v>774</v>
       </c>
@@ -15123,7 +15125,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="467" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A467" t="s">
         <v>774</v>
       </c>
@@ -15140,7 +15142,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="468" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A468" t="s">
         <v>774</v>
       </c>
@@ -15157,7 +15159,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="469" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A469" t="s">
         <v>774</v>
       </c>
@@ -15174,7 +15176,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="470" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A470" t="s">
         <v>774</v>
       </c>
@@ -15194,7 +15196,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="471" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A471" t="s">
         <v>774</v>
       </c>
@@ -15214,7 +15216,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="472" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A472" t="s">
         <v>774</v>
       </c>
@@ -15234,7 +15236,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="473" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A473" t="s">
         <v>774</v>
       </c>
@@ -15254,7 +15256,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="474" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A474" t="s">
         <v>774</v>
       </c>
@@ -15274,7 +15276,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="475" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A475" t="s">
         <v>774</v>
       </c>
@@ -15294,7 +15296,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="476" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A476" t="s">
         <v>774</v>
       </c>
@@ -15311,7 +15313,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="477" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
         <v>774</v>
       </c>
@@ -15331,7 +15333,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="478" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A478" t="s">
         <v>774</v>
       </c>
@@ -15351,7 +15353,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="479" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A479" t="s">
         <v>774</v>
       </c>
@@ -15368,7 +15370,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="480" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A480" t="s">
         <v>774</v>
       </c>
@@ -15388,7 +15390,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="481" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A481" t="s">
         <v>774</v>
       </c>
@@ -15408,7 +15410,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="482" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A482" t="s">
         <v>774</v>
       </c>
@@ -15425,7 +15427,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="483" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A483" t="s">
         <v>774</v>
       </c>
@@ -15442,7 +15444,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="484" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
         <v>774</v>
       </c>
@@ -15462,7 +15464,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="485" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A485" t="s">
         <v>774</v>
       </c>
@@ -15482,7 +15484,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="486" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A486" t="s">
         <v>774</v>
       </c>
@@ -15502,7 +15504,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="487" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A487" t="s">
         <v>774</v>
       </c>
@@ -15519,7 +15521,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="488" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A488" t="s">
         <v>774</v>
       </c>
@@ -15539,7 +15541,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="489" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A489" t="s">
         <v>774</v>
       </c>
@@ -15559,7 +15561,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="490" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A490" t="s">
         <v>774</v>
       </c>
@@ -15579,7 +15581,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="491" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A491" t="s">
         <v>774</v>
       </c>
@@ -15599,7 +15601,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="492" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A492" t="s">
         <v>774</v>
       </c>
@@ -15616,7 +15618,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="493" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A493" t="s">
         <v>774</v>
       </c>
@@ -15633,7 +15635,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="494" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A494" t="s">
         <v>774</v>
       </c>
@@ -15650,7 +15652,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="495" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A495" t="s">
         <v>774</v>
       </c>
@@ -15667,7 +15669,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="496" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A496" t="s">
         <v>774</v>
       </c>
@@ -15684,7 +15686,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="497" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A497" t="s">
         <v>774</v>
       </c>
@@ -15701,7 +15703,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="498" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A498" t="s">
         <v>774</v>
       </c>
@@ -15718,7 +15720,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="499" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A499" t="s">
         <v>774</v>
       </c>
@@ -15735,7 +15737,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="500" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A500" t="s">
         <v>774</v>
       </c>
@@ -15752,7 +15754,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="501" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A501" t="s">
         <v>774</v>
       </c>
@@ -15769,7 +15771,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="502" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A502" t="s">
         <v>774</v>
       </c>
@@ -15786,7 +15788,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="503" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A503" t="s">
         <v>774</v>
       </c>
@@ -15803,7 +15805,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="504" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A504" t="s">
         <v>774</v>
       </c>
@@ -15820,7 +15822,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="505" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A505" t="s">
         <v>774</v>
       </c>
@@ -15837,7 +15839,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="506" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A506" t="s">
         <v>774</v>
       </c>
@@ -15854,7 +15856,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="507" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A507" t="s">
         <v>774</v>
       </c>
@@ -15871,7 +15873,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="508" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A508" t="s">
         <v>774</v>
       </c>
@@ -15888,7 +15890,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="509" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A509" t="s">
         <v>774</v>
       </c>
@@ -15905,7 +15907,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="510" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A510" t="s">
         <v>774</v>
       </c>
@@ -15922,7 +15924,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="511" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A511" t="s">
         <v>774</v>
       </c>
@@ -15939,7 +15941,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="512" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A512" t="s">
         <v>774</v>
       </c>
@@ -15956,7 +15958,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="513" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A513" t="s">
         <v>774</v>
       </c>
@@ -15973,7 +15975,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="514" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A514" t="s">
         <v>774</v>
       </c>
@@ -15990,7 +15992,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="515" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A515" t="s">
         <v>774</v>
       </c>
@@ -16007,7 +16009,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="516" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A516" t="s">
         <v>774</v>
       </c>
@@ -16024,7 +16026,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="517" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A517" t="s">
         <v>774</v>
       </c>
@@ -16041,7 +16043,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="518" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A518" t="s">
         <v>774</v>
       </c>
@@ -16058,7 +16060,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="519" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A519" t="s">
         <v>774</v>
       </c>
@@ -16075,7 +16077,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="520" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A520" t="s">
         <v>774</v>
       </c>
@@ -16092,7 +16094,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="521" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A521" t="s">
         <v>774</v>
       </c>
@@ -16109,7 +16111,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="522" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A522" t="s">
         <v>774</v>
       </c>
@@ -16126,7 +16128,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="523" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A523" t="s">
         <v>774</v>
       </c>
@@ -16143,7 +16145,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="524" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A524" t="s">
         <v>774</v>
       </c>
@@ -16160,7 +16162,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="525" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A525" t="s">
         <v>774</v>
       </c>
@@ -16177,7 +16179,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="526" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A526" t="s">
         <v>774</v>
       </c>
@@ -16194,7 +16196,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="527" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A527" t="s">
         <v>1055</v>
       </c>
@@ -16208,7 +16210,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="528" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:6" hidden="1" x14ac:dyDescent="0.2">
       <c r="A528" t="s">
         <v>1055</v>
       </c>
@@ -16222,7 +16224,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="529" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A529" t="s">
         <v>1055</v>
       </c>
@@ -16236,7 +16238,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="530" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A530" t="s">
         <v>1055</v>
       </c>
@@ -16253,7 +16255,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="531" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A531" t="s">
         <v>1055</v>
       </c>
@@ -16267,7 +16269,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="532" spans="1:5" ht="13.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:5" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A532" t="s">
         <v>1055</v>
       </c>
@@ -16284,7 +16286,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="533" spans="1:5" ht="13.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:5" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A533" t="s">
         <v>1055</v>
       </c>
@@ -16298,7 +16300,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="534" spans="1:5" ht="13.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:5" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A534" t="s">
         <v>1055</v>
       </c>
@@ -16312,7 +16314,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="535" spans="1:5" ht="13.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:5" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A535" t="s">
         <v>1055</v>
       </c>
@@ -16329,7 +16331,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="536" spans="1:5" ht="13.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:5" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A536" t="s">
         <v>1055</v>
       </c>
@@ -16343,7 +16345,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="537" spans="1:5" ht="13.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:5" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A537" t="s">
         <v>1055</v>
       </c>
@@ -16357,7 +16359,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="538" spans="1:5" ht="13.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:5" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A538" t="s">
         <v>1055</v>
       </c>
@@ -16371,7 +16373,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="539" spans="1:5" ht="13.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:5" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A539" t="s">
         <v>1055</v>
       </c>
@@ -16388,7 +16390,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="540" spans="1:5" ht="13.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:5" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A540" t="s">
         <v>1055</v>
       </c>
@@ -16402,7 +16404,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="541" spans="1:5" ht="13.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:5" ht="13.9" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A541" t="s">
         <v>1055</v>
       </c>
@@ -16416,7 +16418,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="542" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A542" t="s">
         <v>1055</v>
       </c>
@@ -16433,7 +16435,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="543" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A543" t="s">
         <v>1055</v>
       </c>
@@ -16447,7 +16449,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="544" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:5" hidden="1" x14ac:dyDescent="0.2">
       <c r="A544" t="s">
         <v>1055</v>
       </c>
@@ -16461,7 +16463,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="545" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A545" t="s">
         <v>1055</v>
       </c>
@@ -16478,7 +16480,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="546" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A546" t="s">
         <v>1055</v>
       </c>
@@ -16492,7 +16494,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="547" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A547" t="s">
         <v>1055</v>
       </c>
@@ -16509,7 +16511,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="548" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A548" t="s">
         <v>1055</v>
       </c>
@@ -16523,7 +16525,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="549" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A549" t="s">
         <v>1055</v>
       </c>
@@ -16537,7 +16539,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="550" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A550" t="s">
         <v>1055</v>
       </c>
@@ -16554,7 +16556,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="551" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A551" t="s">
         <v>1055</v>
       </c>
@@ -16568,7 +16570,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="552" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A552" t="s">
         <v>1055</v>
       </c>
@@ -16585,7 +16587,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="553" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A553" t="s">
         <v>1055</v>
       </c>
@@ -16602,7 +16604,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="554" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A554" t="s">
         <v>1055</v>
       </c>
@@ -16616,7 +16618,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="555" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A555" t="s">
         <v>1055</v>
       </c>
@@ -16630,7 +16632,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="556" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A556" t="s">
         <v>1055</v>
       </c>
@@ -16647,7 +16649,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="557" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A557" t="s">
         <v>1145</v>
       </c>
@@ -16667,7 +16669,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="558" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
         <v>1145</v>
       </c>
@@ -16687,7 +16689,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="559" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
         <v>1145</v>
       </c>
@@ -16707,7 +16709,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="560" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A560" t="s">
         <v>1145</v>
       </c>
@@ -16727,7 +16729,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="561" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A561" t="s">
         <v>1145</v>
       </c>
@@ -16747,7 +16749,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="562" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A562" t="s">
         <v>1145</v>
       </c>
@@ -16767,7 +16769,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="563" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A563" t="s">
         <v>1145</v>
       </c>
@@ -16787,7 +16789,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="564" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A564" t="s">
         <v>1145</v>
       </c>
@@ -16807,7 +16809,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="565" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A565" t="s">
         <v>1145</v>
       </c>
@@ -16827,7 +16829,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="566" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A566" t="s">
         <v>1145</v>
       </c>
@@ -16847,7 +16849,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="567" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A567" t="s">
         <v>1145</v>
       </c>
@@ -16867,7 +16869,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="568" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A568" t="s">
         <v>1145</v>
       </c>
@@ -16887,7 +16889,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="569" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A569" t="s">
         <v>1145</v>
       </c>
@@ -16907,7 +16909,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="570" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A570" t="s">
         <v>1145</v>
       </c>
@@ -16927,7 +16929,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="571" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A571" t="s">
         <v>1145</v>
       </c>
@@ -16947,7 +16949,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="572" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A572" t="s">
         <v>1145</v>
       </c>
@@ -16967,7 +16969,7 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="573" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A573" t="s">
         <v>1145</v>
       </c>
@@ -16987,7 +16989,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="574" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A574" t="s">
         <v>1145</v>
       </c>
@@ -17007,7 +17009,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="575" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A575" t="s">
         <v>1145</v>
       </c>
@@ -17027,7 +17029,7 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="576" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A576" t="s">
         <v>1145</v>
       </c>
@@ -17047,7 +17049,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="577" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A577" t="s">
         <v>1145</v>
       </c>
@@ -17067,7 +17069,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="578" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A578" t="s">
         <v>1145</v>
       </c>
@@ -17087,7 +17089,7 @@
         <v>1186</v>
       </c>
     </row>
-    <row r="579" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A579" t="s">
         <v>1145</v>
       </c>
@@ -17107,7 +17109,7 @@
         <v>1188</v>
       </c>
     </row>
-    <row r="580" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A580" t="s">
         <v>1145</v>
       </c>
@@ -17127,7 +17129,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="581" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A581" t="s">
         <v>1145</v>
       </c>
@@ -17147,7 +17149,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="582" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A582" t="s">
         <v>1145</v>
       </c>
@@ -17167,7 +17169,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="583" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A583" t="s">
         <v>1145</v>
       </c>
@@ -17187,7 +17189,7 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="584" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A584" t="s">
         <v>1145</v>
       </c>
@@ -17207,7 +17209,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="585" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A585" t="s">
         <v>1145</v>
       </c>
@@ -17227,7 +17229,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="586" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A586" t="s">
         <v>1145</v>
       </c>
@@ -17247,7 +17249,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="587" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A587" t="s">
         <v>1145</v>
       </c>
@@ -17267,7 +17269,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="588" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A588" t="s">
         <v>1145</v>
       </c>
@@ -17287,7 +17289,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="589" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A589" t="s">
         <v>1145</v>
       </c>
@@ -17307,7 +17309,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="590" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A590" t="s">
         <v>1145</v>
       </c>
@@ -17327,7 +17329,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="591" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A591" t="s">
         <v>1145</v>
       </c>
@@ -17347,7 +17349,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="592" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A592" t="s">
         <v>1145</v>
       </c>
@@ -17367,7 +17369,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="593" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A593" t="s">
         <v>1145</v>
       </c>
@@ -17387,7 +17389,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="594" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A594" t="s">
         <v>1145</v>
       </c>
@@ -17407,7 +17409,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="595" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A595" t="s">
         <v>1145</v>
       </c>
@@ -17427,7 +17429,7 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="596" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A596" t="s">
         <v>1145</v>
       </c>
@@ -17447,7 +17449,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="597" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A597" t="s">
         <v>1145</v>
       </c>
@@ -17467,7 +17469,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="598" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:8" hidden="1" x14ac:dyDescent="0.2">
       <c r="A598" t="s">
         <v>1145</v>
       </c>
@@ -17487,287 +17489,294 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="599" spans="1:7" ht="19" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A599" t="s">
         <v>1209</v>
       </c>
       <c r="B599" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C599" t="s">
         <v>1210</v>
       </c>
-      <c r="C599" t="s">
+      <c r="D599" s="1" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F599" t="s">
+        <v>1212</v>
+      </c>
+      <c r="G599" t="s">
         <v>1211</v>
       </c>
-      <c r="D599" t="s">
-        <v>1212</v>
-      </c>
-      <c r="F599" t="s">
-        <v>1213</v>
-      </c>
-      <c r="G599" s="1" t="s">
-        <v>1214</v>
-      </c>
-    </row>
-    <row r="600" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H599" s="1"/>
+    </row>
+    <row r="600" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A600" t="s">
         <v>1209</v>
       </c>
       <c r="B600" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C600" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D600" t="s">
         <v>1215</v>
       </c>
-      <c r="D600" t="s">
+      <c r="F600" t="s">
         <v>1212</v>
       </c>
-      <c r="F600" t="s">
-        <v>1213</v>
-      </c>
       <c r="G600" t="s">
-        <v>1216</v>
-      </c>
-    </row>
-    <row r="601" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="601" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A601" t="s">
         <v>1209</v>
       </c>
       <c r="B601" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C601" t="s">
+        <v>1216</v>
+      </c>
+      <c r="D601" t="s">
         <v>1217</v>
       </c>
-      <c r="D601" t="s">
+      <c r="F601" t="s">
         <v>1212</v>
       </c>
-      <c r="F601" t="s">
-        <v>1213</v>
-      </c>
       <c r="G601" t="s">
-        <v>1218</v>
-      </c>
-    </row>
-    <row r="602" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="602" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A602" t="s">
         <v>1209</v>
       </c>
       <c r="B602" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C602" t="s">
+        <v>1218</v>
+      </c>
+      <c r="D602" t="s">
         <v>1219</v>
       </c>
-      <c r="D602" t="s">
+      <c r="F602" t="s">
         <v>1212</v>
       </c>
-      <c r="F602" t="s">
-        <v>1213</v>
-      </c>
       <c r="G602" t="s">
-        <v>1220</v>
-      </c>
-    </row>
-    <row r="603" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="603" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A603" t="s">
         <v>1209</v>
       </c>
       <c r="B603" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C603" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D603" t="s">
         <v>1221</v>
       </c>
-      <c r="D603" t="s">
+      <c r="F603" t="s">
         <v>1212</v>
       </c>
-      <c r="F603" t="s">
-        <v>1213</v>
-      </c>
       <c r="G603" t="s">
-        <v>1222</v>
-      </c>
-    </row>
-    <row r="604" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="604" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A604" t="s">
         <v>1209</v>
       </c>
       <c r="B604" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C604" t="s">
+        <v>1222</v>
+      </c>
+      <c r="D604" t="s">
         <v>1223</v>
       </c>
-      <c r="D604" t="s">
+      <c r="F604" t="s">
         <v>1212</v>
       </c>
-      <c r="F604" t="s">
-        <v>1213</v>
-      </c>
       <c r="G604" t="s">
-        <v>1224</v>
-      </c>
-    </row>
-    <row r="605" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="605" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A605" t="s">
         <v>1209</v>
       </c>
       <c r="B605" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C605" t="s">
+        <v>1224</v>
+      </c>
+      <c r="D605" t="s">
         <v>1225</v>
       </c>
-      <c r="D605" t="s">
+      <c r="F605" t="s">
         <v>1212</v>
       </c>
-      <c r="F605" t="s">
-        <v>1213</v>
-      </c>
       <c r="G605" t="s">
-        <v>1226</v>
-      </c>
-    </row>
-    <row r="606" spans="1:7" ht="84" x14ac:dyDescent="0.3">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="606" spans="1:8" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A606" t="s">
         <v>1209</v>
       </c>
       <c r="B606" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C606" t="s">
+        <v>1226</v>
+      </c>
+      <c r="D606" s="1" t="s">
         <v>1227</v>
       </c>
-      <c r="D606" t="s">
+      <c r="F606" t="s">
         <v>1212</v>
       </c>
-      <c r="F606" t="s">
-        <v>1213</v>
-      </c>
-      <c r="G606" s="1" t="s">
-        <v>1228</v>
-      </c>
-    </row>
-    <row r="607" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G606" t="s">
+        <v>1211</v>
+      </c>
+      <c r="H606" s="1"/>
+    </row>
+    <row r="607" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A607" t="s">
         <v>1209</v>
       </c>
       <c r="B607" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C607" t="s">
+        <v>1228</v>
+      </c>
+      <c r="D607" t="s">
         <v>1229</v>
       </c>
-      <c r="D607" t="s">
+      <c r="F607" t="s">
         <v>1212</v>
       </c>
-      <c r="F607" t="s">
-        <v>1213</v>
-      </c>
       <c r="G607" t="s">
-        <v>1230</v>
-      </c>
-    </row>
-    <row r="608" spans="1:7" ht="56" x14ac:dyDescent="0.3">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="608" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A608" t="s">
         <v>1209</v>
       </c>
       <c r="B608" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C608" t="s">
+        <v>1230</v>
+      </c>
+      <c r="D608" s="1" t="s">
+        <v>1232</v>
+      </c>
+      <c r="F608" t="s">
+        <v>1212</v>
+      </c>
+      <c r="G608" t="s">
         <v>1231</v>
       </c>
-      <c r="D608" t="s">
-        <v>1232</v>
-      </c>
-      <c r="F608" t="s">
-        <v>1213</v>
-      </c>
-      <c r="G608" s="1" t="s">
-        <v>1233</v>
-      </c>
-    </row>
-    <row r="609" spans="1:7" ht="84" x14ac:dyDescent="0.3">
+      <c r="H608" s="1"/>
+    </row>
+    <row r="609" spans="1:8" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A609" t="s">
         <v>1209</v>
       </c>
       <c r="B609" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C609" t="s">
+        <v>1233</v>
+      </c>
+      <c r="D609" s="1" t="s">
         <v>1234</v>
       </c>
-      <c r="D609" t="s">
-        <v>1232</v>
-      </c>
       <c r="F609" t="s">
-        <v>1213</v>
-      </c>
-      <c r="G609" s="1" t="s">
-        <v>1235</v>
-      </c>
-    </row>
-    <row r="610" spans="1:7" ht="196" x14ac:dyDescent="0.3">
+        <v>1212</v>
+      </c>
+      <c r="G609" t="s">
+        <v>1231</v>
+      </c>
+      <c r="H609" s="1"/>
+    </row>
+    <row r="610" spans="1:8" ht="171" x14ac:dyDescent="0.2">
       <c r="A610" t="s">
         <v>1209</v>
       </c>
       <c r="B610" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C610" t="s">
+        <v>1235</v>
+      </c>
+      <c r="D610" s="1" t="s">
         <v>1236</v>
       </c>
-      <c r="D610" t="s">
-        <v>1232</v>
-      </c>
       <c r="F610" t="s">
-        <v>1213</v>
-      </c>
-      <c r="G610" s="1" t="s">
-        <v>1237</v>
-      </c>
-    </row>
-    <row r="611" spans="1:7" ht="154" x14ac:dyDescent="0.3">
+        <v>1212</v>
+      </c>
+      <c r="G610" t="s">
+        <v>1231</v>
+      </c>
+      <c r="H610" s="1"/>
+    </row>
+    <row r="611" spans="1:8" ht="142.5" x14ac:dyDescent="0.2">
       <c r="A611" t="s">
         <v>1209</v>
       </c>
       <c r="B611" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C611" t="s">
+        <v>1237</v>
+      </c>
+      <c r="D611" s="1" t="s">
         <v>1238</v>
       </c>
-      <c r="D611" t="s">
-        <v>1232</v>
-      </c>
       <c r="F611" t="s">
-        <v>1213</v>
-      </c>
-      <c r="G611" s="1" t="s">
-        <v>1239</v>
-      </c>
-    </row>
-    <row r="612" spans="1:7" ht="42" x14ac:dyDescent="0.3">
+        <v>1212</v>
+      </c>
+      <c r="G611" t="s">
+        <v>1231</v>
+      </c>
+      <c r="H611" s="1"/>
+    </row>
+    <row r="612" spans="1:8" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A612" t="s">
         <v>1209</v>
       </c>
       <c r="B612" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C612" t="s">
+        <v>1239</v>
+      </c>
+      <c r="D612" s="1" t="s">
         <v>1240</v>
       </c>
-      <c r="D612" t="s">
-        <v>1232</v>
-      </c>
       <c r="F612" t="s">
-        <v>1213</v>
-      </c>
-      <c r="G612" s="1" t="s">
-        <v>1241</v>
-      </c>
-    </row>
-    <row r="613" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1212</v>
+      </c>
+      <c r="G612" t="s">
+        <v>1231</v>
+      </c>
+      <c r="H612" s="1"/>
+    </row>
+    <row r="613" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A613" t="s">
         <v>1209</v>
       </c>
@@ -17775,19 +17784,19 @@
         <v>5</v>
       </c>
       <c r="C613" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="D613" t="s">
         <v>1243</v>
       </c>
       <c r="F613" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G613" t="s">
-        <v>1244</v>
-      </c>
-    </row>
-    <row r="614" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="614" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A614" t="s">
         <v>1209</v>
       </c>
@@ -17795,19 +17804,19 @@
         <v>5</v>
       </c>
       <c r="C614" t="s">
+        <v>1244</v>
+      </c>
+      <c r="D614" t="s">
         <v>1245</v>
       </c>
-      <c r="D614" t="s">
-        <v>1243</v>
-      </c>
       <c r="F614" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G614" t="s">
-        <v>1246</v>
-      </c>
-    </row>
-    <row r="615" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="615" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A615" t="s">
         <v>1209</v>
       </c>
@@ -17815,19 +17824,19 @@
         <v>5</v>
       </c>
       <c r="C615" t="s">
+        <v>1246</v>
+      </c>
+      <c r="D615" t="s">
         <v>1247</v>
       </c>
-      <c r="D615" t="s">
-        <v>1243</v>
-      </c>
       <c r="F615" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G615" t="s">
-        <v>1248</v>
-      </c>
-    </row>
-    <row r="616" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="616" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A616" t="s">
         <v>1209</v>
       </c>
@@ -17835,19 +17844,19 @@
         <v>5</v>
       </c>
       <c r="C616" t="s">
+        <v>1248</v>
+      </c>
+      <c r="D616" t="s">
         <v>1249</v>
       </c>
-      <c r="D616" t="s">
-        <v>1243</v>
-      </c>
       <c r="F616" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G616" t="s">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="617" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="617" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A617" t="s">
         <v>1209</v>
       </c>
@@ -17855,1279 +17864,1279 @@
         <v>5</v>
       </c>
       <c r="C617" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D617" t="s">
         <v>1251</v>
       </c>
-      <c r="D617" t="s">
-        <v>1243</v>
-      </c>
       <c r="F617" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G617" t="s">
-        <v>1252</v>
-      </c>
-    </row>
-    <row r="618" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="618" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A618" t="s">
         <v>1209</v>
       </c>
       <c r="B618" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C618" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="D618" t="s">
         <v>1254</v>
       </c>
       <c r="F618" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G618" t="s">
-        <v>1255</v>
-      </c>
-    </row>
-    <row r="619" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="619" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A619" t="s">
         <v>1209</v>
       </c>
       <c r="B619" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C619" t="s">
+        <v>1255</v>
+      </c>
+      <c r="D619" t="s">
         <v>1256</v>
       </c>
-      <c r="D619" t="s">
-        <v>1254</v>
-      </c>
       <c r="F619" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G619" t="s">
-        <v>1257</v>
-      </c>
-    </row>
-    <row r="620" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="620" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A620" t="s">
         <v>1209</v>
       </c>
       <c r="B620" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C620" t="s">
+        <v>1257</v>
+      </c>
+      <c r="D620" t="s">
         <v>1258</v>
       </c>
-      <c r="D620" t="s">
-        <v>1254</v>
-      </c>
       <c r="F620" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G620" t="s">
-        <v>1259</v>
-      </c>
-    </row>
-    <row r="621" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="621" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A621" t="s">
         <v>1209</v>
       </c>
       <c r="B621" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C621" t="s">
+        <v>1259</v>
+      </c>
+      <c r="D621" t="s">
         <v>1260</v>
       </c>
-      <c r="D621" t="s">
-        <v>1254</v>
-      </c>
       <c r="F621" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G621" t="s">
-        <v>1261</v>
-      </c>
-    </row>
-    <row r="622" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="622" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A622" t="s">
         <v>1209</v>
       </c>
       <c r="B622" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C622" t="s">
+        <v>1261</v>
+      </c>
+      <c r="D622" t="s">
         <v>1262</v>
       </c>
-      <c r="D622" t="s">
-        <v>1254</v>
-      </c>
       <c r="F622" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G622" t="s">
-        <v>1263</v>
-      </c>
-    </row>
-    <row r="623" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="623" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A623" t="s">
         <v>1209</v>
       </c>
       <c r="B623" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C623" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="D623" t="s">
         <v>1265</v>
       </c>
       <c r="F623" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G623" t="s">
-        <v>1266</v>
-      </c>
-    </row>
-    <row r="624" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="624" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A624" t="s">
         <v>1209</v>
       </c>
       <c r="B624" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C624" t="s">
+        <v>1266</v>
+      </c>
+      <c r="D624" t="s">
         <v>1267</v>
       </c>
-      <c r="D624" t="s">
-        <v>1265</v>
-      </c>
       <c r="F624" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G624" t="s">
-        <v>1268</v>
-      </c>
-    </row>
-    <row r="625" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="625" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A625" t="s">
         <v>1209</v>
       </c>
       <c r="B625" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C625" t="s">
+        <v>1268</v>
+      </c>
+      <c r="D625" t="s">
         <v>1269</v>
       </c>
-      <c r="D625" t="s">
-        <v>1265</v>
-      </c>
       <c r="F625" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G625" t="s">
-        <v>1270</v>
-      </c>
-    </row>
-    <row r="626" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="626" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A626" t="s">
         <v>1209</v>
       </c>
       <c r="B626" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C626" t="s">
+        <v>1270</v>
+      </c>
+      <c r="D626" t="s">
         <v>1271</v>
       </c>
-      <c r="D626" t="s">
-        <v>1265</v>
-      </c>
       <c r="F626" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G626" t="s">
-        <v>1272</v>
-      </c>
-    </row>
-    <row r="627" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="627" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A627" t="s">
         <v>1209</v>
       </c>
       <c r="B627" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C627" t="s">
+        <v>1272</v>
+      </c>
+      <c r="D627" t="s">
         <v>1273</v>
       </c>
-      <c r="D627" t="s">
-        <v>1265</v>
-      </c>
       <c r="F627" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G627" t="s">
-        <v>1274</v>
-      </c>
-    </row>
-    <row r="628" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="628" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A628" t="s">
         <v>1209</v>
       </c>
       <c r="B628" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C628" t="s">
+        <v>1274</v>
+      </c>
+      <c r="D628" t="s">
         <v>1275</v>
       </c>
-      <c r="D628" t="s">
-        <v>1265</v>
-      </c>
       <c r="F628" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G628" t="s">
-        <v>1276</v>
-      </c>
-    </row>
-    <row r="629" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="629" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A629" t="s">
         <v>1209</v>
       </c>
       <c r="B629" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C629" t="s">
+        <v>1276</v>
+      </c>
+      <c r="D629" t="s">
         <v>1277</v>
       </c>
-      <c r="D629" t="s">
-        <v>1265</v>
-      </c>
       <c r="F629" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G629" t="s">
-        <v>1278</v>
-      </c>
-    </row>
-    <row r="630" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="630" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A630" t="s">
         <v>1209</v>
       </c>
       <c r="B630" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C630" t="s">
+        <v>1278</v>
+      </c>
+      <c r="D630" t="s">
         <v>1279</v>
       </c>
-      <c r="D630" t="s">
-        <v>1265</v>
-      </c>
       <c r="F630" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G630" t="s">
-        <v>1280</v>
-      </c>
-    </row>
-    <row r="631" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="631" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A631" t="s">
         <v>1209</v>
       </c>
       <c r="B631" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C631" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="D631" t="s">
         <v>1282</v>
       </c>
       <c r="F631" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G631" t="s">
-        <v>1283</v>
-      </c>
-    </row>
-    <row r="632" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="632" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A632" t="s">
         <v>1209</v>
       </c>
       <c r="B632" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C632" t="s">
+        <v>1283</v>
+      </c>
+      <c r="D632" t="s">
         <v>1284</v>
       </c>
-      <c r="D632" t="s">
-        <v>1282</v>
-      </c>
       <c r="F632" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G632" t="s">
-        <v>1285</v>
-      </c>
-    </row>
-    <row r="633" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="633" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A633" t="s">
         <v>1209</v>
       </c>
       <c r="B633" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C633" t="s">
+        <v>1285</v>
+      </c>
+      <c r="D633" t="s">
         <v>1286</v>
       </c>
-      <c r="D633" t="s">
-        <v>1282</v>
-      </c>
       <c r="F633" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G633" t="s">
-        <v>1287</v>
-      </c>
-    </row>
-    <row r="634" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="634" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A634" t="s">
         <v>1209</v>
       </c>
       <c r="B634" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C634" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="D634" t="s">
         <v>1289</v>
       </c>
       <c r="F634" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G634" t="s">
-        <v>1290</v>
-      </c>
-    </row>
-    <row r="635" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="635" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A635" t="s">
         <v>1209</v>
       </c>
       <c r="B635" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C635" t="s">
+        <v>1290</v>
+      </c>
+      <c r="D635" t="s">
         <v>1291</v>
       </c>
-      <c r="D635" t="s">
-        <v>1289</v>
-      </c>
       <c r="F635" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G635" t="s">
-        <v>1292</v>
-      </c>
-    </row>
-    <row r="636" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="636" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A636" t="s">
         <v>1209</v>
       </c>
       <c r="B636" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C636" t="s">
+        <v>1292</v>
+      </c>
+      <c r="D636" t="s">
         <v>1293</v>
       </c>
-      <c r="D636" t="s">
-        <v>1289</v>
-      </c>
       <c r="F636" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G636" t="s">
-        <v>1294</v>
-      </c>
-    </row>
-    <row r="637" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="637" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A637" t="s">
         <v>1209</v>
       </c>
       <c r="B637" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C637" t="s">
+        <v>1294</v>
+      </c>
+      <c r="D637" t="s">
         <v>1295</v>
       </c>
-      <c r="D637" t="s">
-        <v>1289</v>
-      </c>
       <c r="F637" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G637" t="s">
-        <v>1296</v>
-      </c>
-    </row>
-    <row r="638" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="638" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A638" t="s">
         <v>1209</v>
       </c>
       <c r="B638" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C638" t="s">
+        <v>1296</v>
+      </c>
+      <c r="D638" t="s">
         <v>1297</v>
       </c>
-      <c r="D638" t="s">
-        <v>1289</v>
-      </c>
       <c r="F638" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G638" t="s">
-        <v>1298</v>
-      </c>
-    </row>
-    <row r="639" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="639" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A639" t="s">
         <v>1209</v>
       </c>
       <c r="B639" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C639" t="s">
+        <v>1298</v>
+      </c>
+      <c r="D639" t="s">
         <v>1299</v>
       </c>
-      <c r="D639" t="s">
-        <v>1289</v>
-      </c>
       <c r="F639" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G639" t="s">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="640" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="640" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A640" t="s">
         <v>1209</v>
       </c>
       <c r="B640" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C640" t="s">
+        <v>1300</v>
+      </c>
+      <c r="D640" t="s">
         <v>1301</v>
       </c>
-      <c r="D640" t="s">
-        <v>1289</v>
-      </c>
       <c r="F640" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G640" t="s">
-        <v>1302</v>
-      </c>
-    </row>
-    <row r="641" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="641" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A641" t="s">
         <v>1209</v>
       </c>
       <c r="B641" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C641" t="s">
+        <v>1302</v>
+      </c>
+      <c r="D641" t="s">
         <v>1303</v>
       </c>
-      <c r="D641" t="s">
-        <v>1289</v>
-      </c>
       <c r="F641" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G641" t="s">
-        <v>1304</v>
-      </c>
-    </row>
-    <row r="642" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="642" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A642" t="s">
         <v>1209</v>
       </c>
       <c r="B642" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C642" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="D642" t="s">
         <v>1306</v>
       </c>
       <c r="F642" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G642" t="s">
-        <v>1307</v>
-      </c>
-    </row>
-    <row r="643" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="643" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A643" t="s">
         <v>1209</v>
       </c>
       <c r="B643" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C643" t="s">
+        <v>1307</v>
+      </c>
+      <c r="D643" t="s">
         <v>1308</v>
       </c>
-      <c r="D643" t="s">
-        <v>1306</v>
-      </c>
       <c r="F643" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G643" t="s">
-        <v>1309</v>
-      </c>
-    </row>
-    <row r="644" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="644" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A644" t="s">
         <v>1209</v>
       </c>
       <c r="B644" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C644" t="s">
+        <v>1309</v>
+      </c>
+      <c r="D644" t="s">
         <v>1310</v>
       </c>
-      <c r="D644" t="s">
-        <v>1306</v>
-      </c>
       <c r="F644" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G644" t="s">
-        <v>1311</v>
-      </c>
-    </row>
-    <row r="645" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="645" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A645" t="s">
         <v>1209</v>
       </c>
       <c r="B645" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C645" t="s">
+        <v>1311</v>
+      </c>
+      <c r="D645" t="s">
         <v>1312</v>
       </c>
-      <c r="D645" t="s">
-        <v>1306</v>
-      </c>
       <c r="F645" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G645" t="s">
-        <v>1313</v>
-      </c>
-    </row>
-    <row r="646" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="646" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A646" t="s">
         <v>1209</v>
       </c>
       <c r="B646" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C646" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D646" t="s">
         <v>1314</v>
       </c>
-      <c r="D646" t="s">
-        <v>1306</v>
-      </c>
       <c r="F646" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G646" t="s">
-        <v>1315</v>
-      </c>
-    </row>
-    <row r="647" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="647" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A647" t="s">
         <v>1209</v>
       </c>
       <c r="B647" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C647" t="s">
+        <v>1315</v>
+      </c>
+      <c r="D647" t="s">
         <v>1316</v>
       </c>
-      <c r="D647" t="s">
-        <v>1306</v>
-      </c>
       <c r="F647" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G647" t="s">
-        <v>1317</v>
-      </c>
-    </row>
-    <row r="648" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="648" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A648" t="s">
         <v>1209</v>
       </c>
       <c r="B648" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C648" t="s">
+        <v>1317</v>
+      </c>
+      <c r="D648" t="s">
         <v>1318</v>
       </c>
-      <c r="D648" t="s">
-        <v>1306</v>
-      </c>
       <c r="F648" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G648" t="s">
-        <v>1319</v>
-      </c>
-    </row>
-    <row r="649" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="649" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A649" t="s">
         <v>1209</v>
       </c>
       <c r="B649" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C649" t="s">
+        <v>1319</v>
+      </c>
+      <c r="D649" t="s">
         <v>1320</v>
       </c>
-      <c r="D649" t="s">
-        <v>1306</v>
-      </c>
       <c r="F649" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G649" t="s">
-        <v>1321</v>
-      </c>
-    </row>
-    <row r="650" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="650" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A650" t="s">
         <v>1209</v>
       </c>
       <c r="B650" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C650" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D650" t="s">
         <v>1322</v>
       </c>
-      <c r="D650" t="s">
-        <v>1306</v>
-      </c>
       <c r="F650" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G650" t="s">
-        <v>1323</v>
-      </c>
-    </row>
-    <row r="651" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="651" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A651" t="s">
         <v>1209</v>
       </c>
       <c r="B651" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C651" t="s">
+        <v>1323</v>
+      </c>
+      <c r="D651" t="s">
         <v>1324</v>
       </c>
-      <c r="D651" t="s">
-        <v>1306</v>
-      </c>
       <c r="F651" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G651" t="s">
-        <v>1325</v>
-      </c>
-    </row>
-    <row r="652" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="652" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A652" t="s">
         <v>1209</v>
       </c>
       <c r="B652" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C652" t="s">
+        <v>1325</v>
+      </c>
+      <c r="D652" t="s">
         <v>1326</v>
       </c>
-      <c r="D652" t="s">
-        <v>1306</v>
-      </c>
       <c r="F652" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G652" t="s">
-        <v>1327</v>
-      </c>
-    </row>
-    <row r="653" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="653" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A653" t="s">
         <v>1209</v>
       </c>
       <c r="B653" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C653" t="s">
+        <v>1327</v>
+      </c>
+      <c r="D653" t="s">
         <v>1328</v>
       </c>
-      <c r="D653" t="s">
-        <v>1306</v>
-      </c>
       <c r="F653" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G653" t="s">
-        <v>1329</v>
-      </c>
-    </row>
-    <row r="654" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="654" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A654" t="s">
         <v>1209</v>
       </c>
       <c r="B654" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C654" t="s">
+        <v>1329</v>
+      </c>
+      <c r="D654" t="s">
         <v>1330</v>
       </c>
-      <c r="D654" t="s">
-        <v>1306</v>
-      </c>
       <c r="F654" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G654" t="s">
-        <v>1331</v>
-      </c>
-    </row>
-    <row r="655" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="655" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A655" t="s">
         <v>1209</v>
       </c>
       <c r="B655" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C655" t="s">
+        <v>1331</v>
+      </c>
+      <c r="D655" t="s">
         <v>1332</v>
       </c>
-      <c r="D655" t="s">
-        <v>1306</v>
-      </c>
       <c r="F655" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G655" t="s">
-        <v>1333</v>
-      </c>
-    </row>
-    <row r="656" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="656" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A656" t="s">
         <v>1209</v>
       </c>
       <c r="B656" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C656" t="s">
+        <v>1333</v>
+      </c>
+      <c r="D656" t="s">
         <v>1334</v>
       </c>
-      <c r="D656" t="s">
-        <v>1306</v>
-      </c>
       <c r="F656" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G656" t="s">
-        <v>1335</v>
-      </c>
-    </row>
-    <row r="657" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="657" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A657" t="s">
         <v>1209</v>
       </c>
       <c r="B657" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C657" t="s">
+        <v>1335</v>
+      </c>
+      <c r="D657" t="s">
         <v>1336</v>
       </c>
-      <c r="D657" t="s">
-        <v>1306</v>
-      </c>
       <c r="F657" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G657" t="s">
-        <v>1337</v>
-      </c>
-    </row>
-    <row r="658" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="658" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A658" t="s">
         <v>1209</v>
       </c>
       <c r="B658" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C658" t="s">
+        <v>1337</v>
+      </c>
+      <c r="D658" t="s">
         <v>1338</v>
       </c>
-      <c r="D658" t="s">
-        <v>1306</v>
-      </c>
       <c r="F658" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G658" t="s">
-        <v>1339</v>
-      </c>
-    </row>
-    <row r="659" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="659" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A659" t="s">
         <v>1209</v>
       </c>
       <c r="B659" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C659" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="D659" t="s">
         <v>1341</v>
       </c>
       <c r="F659" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G659" t="s">
-        <v>1342</v>
-      </c>
-    </row>
-    <row r="660" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="660" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A660" t="s">
         <v>1209</v>
       </c>
       <c r="B660" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C660" t="s">
+        <v>1342</v>
+      </c>
+      <c r="D660" t="s">
         <v>1343</v>
       </c>
-      <c r="D660" t="s">
-        <v>1341</v>
-      </c>
       <c r="F660" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G660" t="s">
-        <v>1344</v>
-      </c>
-    </row>
-    <row r="661" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="661" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A661" t="s">
         <v>1209</v>
       </c>
       <c r="B661" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C661" t="s">
+        <v>1344</v>
+      </c>
+      <c r="D661" t="s">
         <v>1345</v>
       </c>
-      <c r="D661" t="s">
-        <v>1341</v>
-      </c>
       <c r="F661" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G661" t="s">
-        <v>1346</v>
-      </c>
-    </row>
-    <row r="662" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="662" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A662" t="s">
         <v>1209</v>
       </c>
       <c r="B662" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C662" t="s">
+        <v>1346</v>
+      </c>
+      <c r="D662" t="s">
         <v>1347</v>
       </c>
-      <c r="D662" t="s">
-        <v>1341</v>
-      </c>
       <c r="F662" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G662" t="s">
-        <v>1348</v>
-      </c>
-    </row>
-    <row r="663" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="663" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A663" t="s">
         <v>1209</v>
       </c>
       <c r="B663" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C663" t="s">
+        <v>1348</v>
+      </c>
+      <c r="D663" t="s">
         <v>1349</v>
       </c>
-      <c r="D663" t="s">
-        <v>1341</v>
-      </c>
       <c r="F663" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G663" t="s">
-        <v>1350</v>
-      </c>
-    </row>
-    <row r="664" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="664" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A664" t="s">
         <v>1209</v>
       </c>
       <c r="B664" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C664" t="s">
+        <v>1350</v>
+      </c>
+      <c r="D664" t="s">
         <v>1351</v>
       </c>
-      <c r="D664" t="s">
-        <v>1341</v>
-      </c>
       <c r="F664" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G664" t="s">
-        <v>1352</v>
-      </c>
-    </row>
-    <row r="665" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="665" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A665" t="s">
         <v>1209</v>
       </c>
       <c r="B665" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C665" t="s">
+        <v>1352</v>
+      </c>
+      <c r="D665" t="s">
         <v>1353</v>
       </c>
-      <c r="D665" t="s">
-        <v>1341</v>
-      </c>
       <c r="F665" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G665" t="s">
-        <v>1354</v>
-      </c>
-    </row>
-    <row r="666" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="666" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A666" t="s">
         <v>1209</v>
       </c>
       <c r="B666" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C666" t="s">
+        <v>1354</v>
+      </c>
+      <c r="D666" t="s">
         <v>1355</v>
       </c>
-      <c r="D666" t="s">
-        <v>1341</v>
-      </c>
       <c r="F666" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G666" t="s">
-        <v>1356</v>
-      </c>
-    </row>
-    <row r="667" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="667" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A667" t="s">
         <v>1209</v>
       </c>
       <c r="B667" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C667" t="s">
+        <v>1356</v>
+      </c>
+      <c r="D667" t="s">
         <v>1357</v>
       </c>
-      <c r="D667" t="s">
-        <v>1341</v>
-      </c>
       <c r="F667" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G667" t="s">
-        <v>1358</v>
-      </c>
-    </row>
-    <row r="668" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="668" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A668" t="s">
         <v>1209</v>
       </c>
       <c r="B668" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C668" t="s">
+        <v>1358</v>
+      </c>
+      <c r="D668" t="s">
         <v>1359</v>
       </c>
-      <c r="D668" t="s">
-        <v>1341</v>
-      </c>
       <c r="F668" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G668" t="s">
-        <v>1360</v>
-      </c>
-    </row>
-    <row r="669" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="669" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A669" t="s">
         <v>1209</v>
       </c>
       <c r="B669" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C669" t="s">
+        <v>1360</v>
+      </c>
+      <c r="D669" t="s">
         <v>1361</v>
       </c>
-      <c r="D669" t="s">
-        <v>1341</v>
-      </c>
       <c r="F669" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G669" t="s">
-        <v>1362</v>
-      </c>
-    </row>
-    <row r="670" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="670" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A670" t="s">
         <v>1209</v>
       </c>
       <c r="B670" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C670" t="s">
+        <v>1362</v>
+      </c>
+      <c r="D670" t="s">
         <v>1363</v>
       </c>
-      <c r="D670" t="s">
-        <v>1341</v>
-      </c>
       <c r="F670" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G670" t="s">
-        <v>1364</v>
-      </c>
-    </row>
-    <row r="671" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="671" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A671" t="s">
         <v>1209</v>
       </c>
       <c r="B671" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C671" t="s">
+        <v>1364</v>
+      </c>
+      <c r="D671" t="s">
         <v>1365</v>
       </c>
-      <c r="D671" t="s">
-        <v>1341</v>
-      </c>
       <c r="F671" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G671" t="s">
-        <v>1366</v>
-      </c>
-    </row>
-    <row r="672" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="672" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A672" t="s">
         <v>1209</v>
       </c>
       <c r="B672" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C672" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D672" t="s">
         <v>1367</v>
       </c>
-      <c r="D672" t="s">
-        <v>1341</v>
-      </c>
       <c r="F672" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G672" t="s">
-        <v>1368</v>
-      </c>
-    </row>
-    <row r="673" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="673" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A673" t="s">
         <v>1209</v>
       </c>
       <c r="B673" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C673" t="s">
+        <v>1368</v>
+      </c>
+      <c r="D673" t="s">
         <v>1369</v>
       </c>
-      <c r="D673" t="s">
-        <v>1341</v>
-      </c>
       <c r="F673" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G673" t="s">
-        <v>1370</v>
-      </c>
-    </row>
-    <row r="674" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="674" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A674" t="s">
         <v>1209</v>
       </c>
       <c r="B674" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C674" t="s">
+        <v>1370</v>
+      </c>
+      <c r="D674" t="s">
         <v>1371</v>
       </c>
-      <c r="D674" t="s">
-        <v>1341</v>
-      </c>
       <c r="F674" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G674" t="s">
-        <v>1372</v>
-      </c>
-    </row>
-    <row r="675" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="675" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A675" t="s">
         <v>1209</v>
       </c>
       <c r="B675" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C675" t="s">
+        <v>1372</v>
+      </c>
+      <c r="D675" t="s">
         <v>1373</v>
       </c>
-      <c r="D675" t="s">
-        <v>1341</v>
-      </c>
       <c r="F675" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G675" t="s">
-        <v>1374</v>
-      </c>
-    </row>
-    <row r="676" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="676" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A676" t="s">
         <v>1209</v>
       </c>
       <c r="B676" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C676" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="D676" t="s">
-        <v>1341</v>
+        <v>1357</v>
       </c>
       <c r="F676" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G676" t="s">
-        <v>1358</v>
-      </c>
-    </row>
-    <row r="677" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="677" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A677" t="s">
         <v>1209</v>
       </c>
       <c r="B677" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C677" t="s">
+        <v>1375</v>
+      </c>
+      <c r="D677" t="s">
         <v>1376</v>
       </c>
-      <c r="D677" t="s">
-        <v>1341</v>
-      </c>
       <c r="F677" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G677" t="s">
-        <v>1377</v>
-      </c>
-    </row>
-    <row r="678" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="678" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A678" t="s">
         <v>1209</v>
       </c>
       <c r="B678" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C678" t="s">
+        <v>1377</v>
+      </c>
+      <c r="D678" t="s">
         <v>1378</v>
       </c>
-      <c r="D678" t="s">
-        <v>1341</v>
-      </c>
       <c r="F678" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G678" t="s">
-        <v>1379</v>
-      </c>
-    </row>
-    <row r="679" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="679" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A679" t="s">
         <v>1209</v>
       </c>
       <c r="B679" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C679" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="D679" t="s">
         <v>1381</v>
       </c>
       <c r="F679" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G679" t="s">
-        <v>1382</v>
-      </c>
-    </row>
-    <row r="680" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="680" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A680" t="s">
         <v>1209</v>
       </c>
       <c r="B680" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C680" t="s">
+        <v>1382</v>
+      </c>
+      <c r="D680" t="s">
         <v>1383</v>
       </c>
-      <c r="D680" t="s">
-        <v>1381</v>
-      </c>
       <c r="F680" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G680" t="s">
-        <v>1384</v>
-      </c>
-    </row>
-    <row r="681" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="681" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A681" t="s">
         <v>1209</v>
       </c>
@@ -19135,19 +19144,19 @@
         <v>286</v>
       </c>
       <c r="C681" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="D681" t="s">
         <v>1386</v>
       </c>
       <c r="F681" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G681" t="s">
-        <v>1387</v>
-      </c>
-    </row>
-    <row r="682" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="682" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A682" t="s">
         <v>1209</v>
       </c>
@@ -19155,19 +19164,19 @@
         <v>286</v>
       </c>
       <c r="C682" t="s">
+        <v>1387</v>
+      </c>
+      <c r="D682" t="s">
         <v>1388</v>
       </c>
-      <c r="D682" t="s">
-        <v>1386</v>
-      </c>
       <c r="F682" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G682" t="s">
-        <v>1389</v>
-      </c>
-    </row>
-    <row r="683" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="683" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A683" t="s">
         <v>1209</v>
       </c>
@@ -19175,79 +19184,79 @@
         <v>286</v>
       </c>
       <c r="C683" t="s">
+        <v>1389</v>
+      </c>
+      <c r="D683" t="s">
         <v>1390</v>
       </c>
-      <c r="D683" t="s">
-        <v>1386</v>
-      </c>
       <c r="F683" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G683" t="s">
-        <v>1391</v>
-      </c>
-    </row>
-    <row r="684" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="684" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A684" t="s">
         <v>1209</v>
       </c>
       <c r="B684" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C684" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="D684" t="s">
         <v>1393</v>
       </c>
       <c r="F684" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G684" t="s">
-        <v>1394</v>
-      </c>
-    </row>
-    <row r="685" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1392</v>
+      </c>
+    </row>
+    <row r="685" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A685" t="s">
         <v>1209</v>
       </c>
       <c r="B685" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C685" t="s">
+        <v>1394</v>
+      </c>
+      <c r="D685" t="s">
         <v>1395</v>
       </c>
-      <c r="D685" t="s">
-        <v>1393</v>
-      </c>
       <c r="F685" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G685" t="s">
-        <v>1396</v>
-      </c>
-    </row>
-    <row r="686" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1392</v>
+      </c>
+    </row>
+    <row r="686" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A686" t="s">
         <v>1209</v>
       </c>
       <c r="B686" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C686" t="s">
+        <v>1396</v>
+      </c>
+      <c r="D686" t="s">
         <v>1397</v>
       </c>
-      <c r="D686" t="s">
-        <v>1393</v>
-      </c>
       <c r="F686" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G686" t="s">
-        <v>1398</v>
-      </c>
-    </row>
-    <row r="687" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1392</v>
+      </c>
+    </row>
+    <row r="687" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A687" t="s">
         <v>1209</v>
       </c>
@@ -19255,19 +19264,19 @@
         <v>286</v>
       </c>
       <c r="C687" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="D687" t="s">
         <v>1400</v>
       </c>
       <c r="F687" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G687" t="s">
-        <v>1401</v>
-      </c>
-    </row>
-    <row r="688" spans="1:7" ht="266" x14ac:dyDescent="0.3">
+        <v>1399</v>
+      </c>
+    </row>
+    <row r="688" spans="1:8" ht="213.75" x14ac:dyDescent="0.2">
       <c r="A688" t="s">
         <v>1209</v>
       </c>
@@ -19275,19 +19284,20 @@
         <v>286</v>
       </c>
       <c r="C688" t="s">
+        <v>1401</v>
+      </c>
+      <c r="D688" s="1" t="s">
         <v>1402</v>
       </c>
-      <c r="D688" t="s">
-        <v>1400</v>
-      </c>
       <c r="F688" t="s">
-        <v>1213</v>
-      </c>
-      <c r="G688" s="1" t="s">
-        <v>1403</v>
-      </c>
-    </row>
-    <row r="689" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1212</v>
+      </c>
+      <c r="G688" t="s">
+        <v>1399</v>
+      </c>
+      <c r="H688" s="1"/>
+    </row>
+    <row r="689" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A689" t="s">
         <v>1209</v>
       </c>
@@ -19295,19 +19305,19 @@
         <v>286</v>
       </c>
       <c r="C689" t="s">
+        <v>1403</v>
+      </c>
+      <c r="D689" t="s">
         <v>1404</v>
       </c>
-      <c r="D689" t="s">
-        <v>1400</v>
-      </c>
       <c r="F689" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G689" t="s">
-        <v>1405</v>
-      </c>
-    </row>
-    <row r="690" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1399</v>
+      </c>
+    </row>
+    <row r="690" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A690" t="s">
         <v>1209</v>
       </c>
@@ -19315,19 +19325,19 @@
         <v>286</v>
       </c>
       <c r="C690" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D690" t="s">
         <v>1406</v>
       </c>
-      <c r="D690" t="s">
-        <v>1400</v>
-      </c>
       <c r="F690" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G690" t="s">
-        <v>1407</v>
-      </c>
-    </row>
-    <row r="691" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1399</v>
+      </c>
+    </row>
+    <row r="691" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A691" t="s">
         <v>1209</v>
       </c>
@@ -19335,19 +19345,19 @@
         <v>286</v>
       </c>
       <c r="C691" t="s">
+        <v>1407</v>
+      </c>
+      <c r="D691" t="s">
         <v>1408</v>
       </c>
-      <c r="D691" t="s">
-        <v>1400</v>
-      </c>
       <c r="F691" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G691" t="s">
-        <v>1409</v>
-      </c>
-    </row>
-    <row r="692" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1399</v>
+      </c>
+    </row>
+    <row r="692" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A692" t="s">
         <v>1209</v>
       </c>
@@ -19355,200 +19365,206 @@
         <v>286</v>
       </c>
       <c r="C692" t="s">
+        <v>1409</v>
+      </c>
+      <c r="D692" t="s">
         <v>1410</v>
       </c>
-      <c r="D692" t="s">
-        <v>1400</v>
-      </c>
       <c r="F692" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G692" t="s">
-        <v>1411</v>
-      </c>
-    </row>
-    <row r="693" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1399</v>
+      </c>
+    </row>
+    <row r="693" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A693" t="s">
         <v>1209</v>
       </c>
       <c r="B693" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C693" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="D693" t="s">
         <v>1413</v>
       </c>
       <c r="F693" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G693" t="s">
-        <v>1414</v>
-      </c>
-    </row>
-    <row r="694" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="694" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A694" t="s">
         <v>1209</v>
       </c>
       <c r="B694" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C694" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D694" t="s">
         <v>1415</v>
       </c>
-      <c r="D694" t="s">
-        <v>1413</v>
-      </c>
       <c r="F694" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G694" t="s">
-        <v>1416</v>
-      </c>
-    </row>
-    <row r="695" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="695" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A695" t="s">
         <v>1209</v>
       </c>
       <c r="B695" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C695" t="s">
+        <v>1416</v>
+      </c>
+      <c r="D695" t="s">
         <v>1417</v>
       </c>
-      <c r="D695" t="s">
-        <v>1413</v>
-      </c>
       <c r="F695" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G695" t="s">
-        <v>1418</v>
-      </c>
-    </row>
-    <row r="696" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="696" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A696" t="s">
         <v>1209</v>
       </c>
       <c r="B696" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C696" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="D696" t="s">
         <v>1420</v>
       </c>
       <c r="F696" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G696" t="s">
-        <v>1421</v>
-      </c>
-    </row>
-    <row r="697" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="697" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A697" t="s">
         <v>1209</v>
       </c>
       <c r="B697" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C697" t="s">
+        <v>1421</v>
+      </c>
+      <c r="D697" t="s">
         <v>1422</v>
       </c>
-      <c r="D697" t="s">
-        <v>1420</v>
-      </c>
       <c r="F697" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G697" t="s">
-        <v>1423</v>
-      </c>
-    </row>
-    <row r="698" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="698" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A698" t="s">
         <v>1209</v>
       </c>
       <c r="B698" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C698" t="s">
+        <v>1423</v>
+      </c>
+      <c r="D698" t="s">
         <v>1424</v>
       </c>
-      <c r="D698" t="s">
-        <v>1420</v>
-      </c>
       <c r="F698" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G698" t="s">
-        <v>1425</v>
-      </c>
-    </row>
-    <row r="699" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="699" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A699" t="s">
         <v>1209</v>
       </c>
       <c r="B699" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C699" t="s">
+        <v>1425</v>
+      </c>
+      <c r="D699" t="s">
         <v>1426</v>
       </c>
-      <c r="D699" t="s">
-        <v>1420</v>
-      </c>
       <c r="F699" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G699" t="s">
-        <v>1427</v>
-      </c>
-    </row>
-    <row r="700" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="700" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A700" t="s">
         <v>1209</v>
       </c>
       <c r="B700" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C700" t="s">
+        <v>1427</v>
+      </c>
+      <c r="D700" t="s">
         <v>1428</v>
       </c>
-      <c r="D700" t="s">
-        <v>1420</v>
-      </c>
       <c r="F700" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G700" t="s">
-        <v>1429</v>
-      </c>
-    </row>
-    <row r="701" spans="1:7" x14ac:dyDescent="0.3">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="701" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A701" t="s">
         <v>1209</v>
       </c>
       <c r="B701" t="s">
-        <v>1210</v>
+        <v>1140</v>
       </c>
       <c r="C701" t="s">
+        <v>1429</v>
+      </c>
+      <c r="D701" t="s">
         <v>1430</v>
       </c>
-      <c r="D701" t="s">
-        <v>1420</v>
-      </c>
       <c r="F701" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="G701" t="s">
-        <v>1431</v>
+        <v>1419</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G569" xr:uid="{4F4B9D16-0649-4346-A6A6-AF198B8A35D8}"/>
+  <autoFilter ref="A1:G701" xr:uid="{4F4B9D16-0649-4346-A6A6-AF198B8A35D8}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="SBTi"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
